--- a/SCRAPING/GAMBAR/hotelV2-htm_updated.xlsx
+++ b/SCRAPING/GAMBAR/hotelV2-htm_updated.xlsx
@@ -494,9 +494,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Selorejo_Hotel_&amp;_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -522,9 +526,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Grand_Pujon_View_Hotel_and_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -550,9 +558,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Panorama</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -578,9 +590,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/PHR_GT2.BALEKAMBANG_PENGINAPAN_PANTAI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -606,9 +622,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_3289_Penginapan_Dita_Family</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -634,9 +654,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/LG_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -662,9 +686,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_KaliBiru</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -690,9 +718,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Sangnala_Homestay_Pakisaji</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -718,9 +750,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/House_of_Melati_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -746,9 +782,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SPOT_ON_90797_Sukun_Syariah_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -774,9 +814,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bromo_Family_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -802,9 +846,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Isro_Guest_House_Syariah_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -830,9 +878,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Condro_Wulan_Hostel</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -858,9 +910,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rayana_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -886,9 +942,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Panderman_Indah</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -914,9 +974,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kanana_Retreat</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -942,9 +1006,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Santoso</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -970,9 +1038,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_Batu_Hotel_&amp;_Villas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -998,9 +1070,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Golden_Tulip_Holland_Resort_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1026,9 +1102,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Family_Hotel_Gradia_2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1054,9 +1134,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Pinky_Guest_House_Hotel_&amp;_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1082,9 +1166,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Kartika_Raya</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1138,9 +1226,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Apache_Camp</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1166,9 +1258,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_Dhilpratis</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1194,9 +1290,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Marry_Ind</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1222,9 +1322,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RORO_Hotel_ꦥꦔꦶꦤꦼꦥꦤ꧀ꦫꦫ</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1250,9 +1354,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Kawi_Surapatha</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1278,9 +1386,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Dua_Dua_Redpartner</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1306,9 +1418,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Jawa_Timur_Park_2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1334,9 +1450,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Urbanview_Hotel_Bubusini_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1390,9 +1510,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Guest_House_Syariah_NusaIndah_2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1418,9 +1542,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Embun_Pagi_Hostel_&amp;_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1446,9 +1574,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_di_Batu__Roemah_YWI</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1474,9 +1606,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Pohon_Inn_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1502,9 +1638,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Omah_Londo_Hotel_Luxury</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1530,9 +1670,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Puncak_Pinus_And_Pool</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1558,9 +1702,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Tiara_Family_Residence_Batu_by_NAP</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1586,9 +1734,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Family_Hotel_Gradia_1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1614,9 +1766,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Mutiara_Panderman_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1642,9 +1798,13 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_near_Batu_Night_Spectacular_3</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1670,9 +1830,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kusuma_Agrowisata_Resort_&amp;_Convention_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1698,9 +1862,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SPOT_ON_1767_Villa_Anggur_Panderman</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1726,9 +1894,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Prima_Asri_153</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1754,9 +1926,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Omahku_Guest_House_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1782,9 +1958,13 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_1194_Villa_Bukit_Panderman_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1810,9 +1990,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lancar_Homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1838,9 +2022,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Batuque_Town_Villa_2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1866,9 +2054,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Seulawah_Resort_&amp;_Cafe</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1894,9 +2086,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/BaliKu_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1922,9 +2118,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Pondok_Wisata_Ilona</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1950,9 +2150,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Amartahills_Hotel_and_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1978,9 +2182,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Alam_Batu_Village</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2006,9 +2214,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Urbanview_Syariah_Kanigara_Guesthouse</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2034,9 +2246,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kontena_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2062,9 +2278,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hidden_Paradiso_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2090,9 +2310,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Seulawah_Grand_View</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2118,9 +2342,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Horison_Trunojoyo</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2146,9 +2374,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Shakila_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2174,9 +2406,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_@_Villa_Bontes_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2202,9 +2438,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bobocabin_Coban_Rondo,_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2230,9 +2470,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SR_Guesthouse</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2258,9 +2502,13 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/HOTEL_GRAND_PALEM</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2286,9 +2534,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Amaranta_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2342,9 +2594,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_near_Balai_Kota_Batu_2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2370,9 +2626,13 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Three_Eight_Front_One_Boutique_Hotel_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2398,9 +2658,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Royal_Hotel_&amp;_Villa_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2426,9 +2690,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Aster</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2454,9 +2722,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/éL_Hotel_Kartika_Wijaya_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2482,9 +2754,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Batu_Permai</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2510,9 +2786,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_Sekar_Gambir</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2538,9 +2818,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_Onsen_Hot_Spring_Resort_Songgoriti</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2566,9 +2850,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_Gafisa_2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2594,9 +2882,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Arumdalu_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2622,9 +2914,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_near_Songgoriti_Temple</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2650,9 +2946,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Trisno_Putra</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2678,9 +2978,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rosetta_Villa_&amp;_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2706,9 +3010,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Vila_BIRU_Songgoriti</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2734,9 +3042,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Waskita</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2762,9 +3074,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Panorama_İnn_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2790,9 +3106,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Gress_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2818,9 +3138,13 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Amigo_2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2846,9 +3170,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Arumdalu_24_A_Songgoriti</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2874,9 +3202,13 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Urbanview_Hotel_Sky_Batu_Malang_by_RedDoorz</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2930,9 +3262,13 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Palem_Sari_Syariah_Batu_RedPartner</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2958,9 +3294,13 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Mustika_Sari_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2986,9 +3326,13 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bata_Merah_Guest_House_&amp;_Camping_Ground</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3014,9 +3358,13 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Spencer_Green_Hotel_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3042,9 +3390,13 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/DeView_Hotel_by_PRO</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3070,9 +3422,13 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Cemara_Resort_&amp;_Cafe</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3098,9 +3454,13 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/d'homestay</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3126,9 +3486,13 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Grand_Miami_Hotel,_Kepanjen</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3154,9 +3518,13 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D'SHARIO_HOTEL</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3182,9 +3550,13 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Losmen_Ryan't</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3238,9 +3610,13 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Indah_Jaya_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3266,9 +3642,13 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_Miki_Gunung_Kawi</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3294,9 +3674,13 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lembah_Indah_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3322,9 +3706,13 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rayz_UMM_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3350,9 +3738,13 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ador_46_Homestay_Syariah_&amp;_Kost_Harian_Kota_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3406,9 +3798,13 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Radho_Syariah_malang</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3462,9 +3858,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lovina_Inn_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3490,9 +3890,13 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Mitra_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3518,9 +3922,13 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RINDANG_Glamping</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3574,9 +3982,13 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Super_OYO_604_Cemara's_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3602,9 +4014,13 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sinergi_Hotel_dan_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3630,9 +4046,13 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Redjeki_Guesthouse_Cafe_Batu_-_Reddoorz_near_Jatim_Park_3</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3658,9 +4078,13 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Grand_Dream_Cita_Mandiri_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3686,9 +4110,13 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_near_Batu_Night_Spectacular</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3714,9 +4142,13 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/GUEST_HOUSE_PALEM_ASRI</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3742,9 +4174,13 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_Kenkei</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3770,9 +4206,13 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_murah_di_batu_malang</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3798,9 +4238,13 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_90828_Ara_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3826,9 +4270,13 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_Farel</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3854,9 +4302,13 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kahan_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3910,9 +4362,13 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Batuque_Town_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3938,9 +4394,13 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Farbel_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3966,9 +4426,13 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Eco_Green_Park_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3994,9 +4458,13 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Rahayu_Guesthouse_RedPartner_near_Jatim_Park_2_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4022,9 +4490,13 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Mama_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4050,9 +4522,13 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Omah_Anin_Guest_House_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4078,9 +4554,13 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Imafa_Inn_RedPartner_near_Jatim_Park_2</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4106,9 +4586,13 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/AKBAR_3_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4134,9 +4618,13 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Batu_View_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4162,9 +4650,13 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Guest_house_syariah_KaGami</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4190,9 +4682,13 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Reddoorz_near_dino_park</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4218,9 +4714,13 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kaluna_Resort_&amp;_Cafe</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4246,9 +4746,13 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Villi</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4274,9 +4778,13 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Family_Homestay_Arya</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4302,9 +4810,13 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/HANSEL_HOMESTAY_Dekat_BNS_Kota_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4358,9 +4870,13 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Grand_Batu_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4386,9 +4902,13 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sea_Villa_Kota_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4414,9 +4934,13 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Alun_Alun_Batu_2</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4442,9 +4966,13 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/THE_HALONA_VILLA_BATU</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4470,9 +4998,13 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Mulya_near_Alun_Alun_Batu_RedPartner</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4498,9 +5030,13 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Harwin_Homestay_Keluarga</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4526,9 +5062,13 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sahabat_Backpacker_1_Alegria_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4554,9 +5094,13 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Pandan_Inn_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4582,9 +5126,13 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Arjuna_Kota_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4610,9 +5158,13 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sahabat_Backpacker_2_Matabean_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4638,9 +5190,13 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Guest_House_180</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4666,9 +5222,13 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Arimbi_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -4694,9 +5254,13 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bayleaf_Guest_House_Syariah_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -4722,9 +5286,13 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Mutiara_Baru</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -4750,9 +5318,13 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/BATU_INDAH_POOL_VILLA</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -4778,9 +5350,13 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sahar_Backpacker</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -4806,9 +5382,13 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Apple_Green_Hotel_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -4834,9 +5414,13 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Pondok_Jatim_Park_Hotel_and_Cafe</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4862,9 +5446,13 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Gendhis_Batu_Boutique_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4890,9 +5478,13 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Tripletree_Ciptaningati_Culture_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4918,9 +5510,13 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Zavier_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4946,9 +5542,13 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_de_Wahyu_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4974,9 +5574,13 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hanoman_Kota_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5002,9 +5606,13 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Purnama_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5030,9 +5638,13 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lembah_Metro_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5058,9 +5670,13 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Wijaya</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5086,9 +5702,13 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Grand_City_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5114,9 +5734,13 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kintamani_360_Villa_&amp;_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5142,9 +5766,13 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Filadelfia_Gallery_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5170,9 +5798,13 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Melinda_Home_Stay</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5198,9 +5830,13 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Oak_Tree_Glamping_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5254,9 +5890,13 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Wisma_Wisata_Wiratama</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5282,9 +5922,13 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
-      </c>
-      <c r="H173" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_New_Handayani_Villa's</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5310,9 +5954,13 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Transformer_Center</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5338,9 +5986,13 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
-      </c>
-      <c r="H175" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Panorama_Villas_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5366,9 +6018,13 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Parama_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5394,9 +6050,13 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Selecta</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5422,9 +6082,13 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sazara_Hotel_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5450,9 +6114,13 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
-      </c>
-      <c r="H179" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Mutu_Edutel</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5478,9 +6146,13 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SAFIRA_HOMESTAY_PANTAI_UNGAPAN</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -5506,9 +6178,13 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/ELTARI_Pine_House</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -5534,9 +6210,13 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_YNO_Castle_Kepanjen</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -5562,9 +6242,13 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
-      </c>
-      <c r="H183" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Core_Inn_Juwita_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -5590,9 +6274,13 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Gerbang_Biru</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -5618,9 +6306,13 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Grand_Kanjuruhan_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -5646,9 +6338,13 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
-      </c>
-      <c r="H186" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Mirabell_Hotel_&amp;_Convention_Hall</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -5674,9 +6370,13 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
-      </c>
-      <c r="H187" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/GRAND_SEMANGGI_HOTEL</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -5702,9 +6402,13 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kos_Griya_Gangsar_Kepanjen_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -5730,9 +6434,13 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
-      </c>
-      <c r="H189" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Joyo_Homestay_Syariah_(penginapan_murah_malang)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -5758,9 +6466,13 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
-      </c>
-      <c r="H190" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_@_Swun_Stay_Raya_Langsep</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -5786,9 +6498,13 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H191" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sigura-Gura_Homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5814,9 +6530,13 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Youkata_Stay_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -5842,9 +6562,13 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Syariah_99_by_VRV</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -5870,9 +6594,13 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Camelia</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -5898,9 +6626,13 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Tya_Family_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -5926,9 +6658,13 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/dinoyo_homestay_syariah</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -5954,9 +6690,13 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_Life_414_Loji_Rejo_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -5982,9 +6722,13 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
-      </c>
-      <c r="H198" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Vintage_58_Penginapan_khusus_wanita</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6010,9 +6754,13 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
-      </c>
-      <c r="H199" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Noura_Guest_House_syariah_merjosari</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -6038,9 +6786,13 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
-      </c>
-      <c r="H200" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Giri_Palma_Villa</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -6066,9 +6818,13 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
-      </c>
-      <c r="H201" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Tidar</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -6094,9 +6850,13 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Hostel_near_Malang_Train_Station_3.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -6122,9 +6882,13 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
-      </c>
-      <c r="H203" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SULFAT_HOMESTAY_Penginapan_Murah_dekat_Stasiun_Kota_Malang_Jalur_Bromo_Dekat_Bandara_Abd_Saleh</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -6150,9 +6914,13 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
-      </c>
-      <c r="H204" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/De'Vita_Family_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6178,9 +6946,13 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SPOT_ON_91530_Sumpil_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -6206,9 +6978,13 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
-      </c>
-      <c r="H206" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Fayfai_homestay_Malang_(Penginapan_di_batu_Malang,_Kos_harian_Malang,_dekat_UMM,_Murah)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6234,9 +7010,13 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
-      </c>
-      <c r="H207" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_O_Symphony_Homestay_Tlogomas</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6262,9 +7042,13 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Gribig_Guest_House_Mitra_RedDoorz</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6290,9 +7074,13 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Tini’s_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6318,9 +7106,13 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Edotel_tebe_syariah</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -6346,9 +7138,13 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_353_Loesje_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -6374,9 +7170,13 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D_Maktab_Syariah_Mitra_RedDoorz_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -6402,9 +7202,13 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/AORI_Guest_House_(Syariah)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -6430,9 +7234,13 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
-      </c>
-      <c r="H214" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_Flagship_90723_Khalifi_House_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -6458,9 +7266,13 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RADZ_&amp;_RASFA_Homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -6486,9 +7298,13 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
-      </c>
-      <c r="H216" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ascent_Premiere_Hotel_and_Convention</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -6514,9 +7330,13 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
-      </c>
-      <c r="H217" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_near_Brawijaya_Museum</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -6542,9 +7362,13 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
-      </c>
-      <c r="H218" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/GUEST_HOUSE_DE_AZKA_STYLE_SYARIAH</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -6570,9 +7394,13 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
-      </c>
-      <c r="H219" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_WoPi</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -6598,9 +7426,13 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kapal_Garden_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -6626,9 +7458,13 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Riuma_Resort__Hotel_Malang__Penginapan_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -6654,9 +7490,13 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0</v>
-      </c>
-      <c r="H222" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Jawa_Timur_Park_3</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -6682,9 +7522,13 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
-      </c>
-      <c r="H223" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_3909_ARG_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -6710,9 +7554,13 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
-      </c>
-      <c r="H224" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/MHS_Inn_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -6738,9 +7586,13 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
-      </c>
-      <c r="H225" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Putri_Utari_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -6766,9 +7618,13 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
-      </c>
-      <c r="H226" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Mentari</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -6794,9 +7650,13 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
-      </c>
-      <c r="H227" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Briggs_Inn_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -6822,9 +7682,13 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
-      </c>
-      <c r="H228" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kalila_Penginapan_di_Batu_Malang_(Dekat_jatimpark_3,_Alun_alun_batu,_Kota_Batu)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -6850,9 +7714,13 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
-      </c>
-      <c r="H229" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Senyum_World_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -6878,9 +7746,13 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_Singhasari_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -6906,9 +7778,13 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
-      </c>
-      <c r="H231" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Azana_BeSt_Hotel_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -6934,9 +7810,13 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
-      </c>
-      <c r="H232" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rumasagara_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6962,9 +7842,13 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
-      </c>
-      <c r="H233" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Maniva_Particael_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -6990,9 +7874,13 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
-      </c>
-      <c r="H234" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Dedaunan_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -7018,9 +7906,13 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
-      </c>
-      <c r="H235" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SUGIH_WARAS_FAMILY_HOMESTAY_&amp;_KOS_HARIAN</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -7046,9 +7938,13 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
-      </c>
-      <c r="H236" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Vanda_Villa_Batu</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -7074,9 +7970,13 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
-      </c>
-      <c r="H237" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_near_Gor_Ken_Arok</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -7102,9 +8002,13 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
-      </c>
-      <c r="H238" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Padi_Heritage_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7130,9 +8034,13 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sofia_Syariah_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -7158,9 +8066,13 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
-      </c>
-      <c r="H240" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Miami_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -7186,9 +8098,13 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
-      </c>
-      <c r="H241" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Great_Star_Premium_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -7214,9 +8130,13 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
-      </c>
-      <c r="H242" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Bukit_Dieng_2</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -7242,9 +8162,13 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/CLASS_Premium_Guest_House_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -7270,9 +8194,13 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
-      </c>
-      <c r="H244" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Home_Stay_Pulosari_Living</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -7298,9 +8226,13 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
-      </c>
-      <c r="H245" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Java_Boutique_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -7326,9 +8258,13 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_815_Double_D9_Guesthouse</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -7354,9 +8290,13 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
-      </c>
-      <c r="H247" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/mcb_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -7410,9 +8350,13 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
-      </c>
-      <c r="H249" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hillside_Suite_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -7438,9 +8382,13 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ijen_Suites_Resort_&amp;_Convention_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -7466,9 +8414,13 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D'Paragon_Bukit_Dieng_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -7494,9 +8446,13 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Aloha_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -7522,9 +8478,13 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/De'Corner_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -7550,9 +8510,13 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0</v>
-      </c>
-      <c r="H254" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Srikandi_Guesthouse</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -7578,9 +8542,13 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
-      </c>
-      <c r="H255" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Tlogomas_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -7606,9 +8574,13 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0</v>
-      </c>
-      <c r="H256" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Family_Guest_House_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -7634,9 +8606,13 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ubud_Cottages_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -7662,9 +8638,13 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0</v>
-      </c>
-      <c r="H258" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Kos_&amp;_Homestay_Villa_Tidar</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -7690,9 +8670,13 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
-      </c>
-      <c r="H259" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Nyaman_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -7718,9 +8702,13 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
-      </c>
-      <c r="H260" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/CLOSEDE_PROP</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -7746,9 +8734,13 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
-      </c>
-      <c r="H261" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_@_Jl_Simpang_Gajayana_(Hasanah_Guest_House_Gajayana)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -7774,9 +8766,13 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_3763_Oq_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -7802,9 +8798,13 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Omahkoe_guesthouse</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -7830,9 +8830,13 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/HOMEY</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -7858,9 +8862,13 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Embun_Pagi_Syariah_Bendungan_Sempor_8_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -7886,9 +8894,13 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_Life_2744_Guest_House_Qudsi</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -7914,9 +8926,13 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0</v>
-      </c>
-      <c r="H267" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Merjosari_Family_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -7942,9 +8958,13 @@
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0</v>
-      </c>
-      <c r="H268" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/New_Bandahara_Exclusive</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -7970,9 +8990,13 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
-      </c>
-      <c r="H269" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Djuragan_Kamar_Bandahara</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -7998,9 +9022,13 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
-      </c>
-      <c r="H270" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ed_Ning_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -8026,9 +9054,13 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
-      </c>
-      <c r="H271" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Adisa_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -8054,9 +9086,13 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Shinta_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -8082,9 +9118,13 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
-      </c>
-      <c r="H273" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Onyo_Sigura-gura_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -8138,9 +9178,13 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/My_Dormy_Hostel_UMM</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -8166,9 +9210,13 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0</v>
-      </c>
-      <c r="H276" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_90480_sultan_palace_guest_house</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -8194,9 +9242,13 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
-      </c>
-      <c r="H277" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sunrise_Resort_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -8222,9 +9274,13 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0</v>
-      </c>
-      <c r="H278" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Forzando_House_Redpartner_near_Universitas_Muhammadiyah_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -8250,9 +9306,13 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
-      </c>
-      <c r="H279" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rosa_Pavilion_Syariah_near_UMM_Redpartner</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -8278,9 +9338,13 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Smart_Tlogomas_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -8306,9 +9370,13 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
-      </c>
-      <c r="H281" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/favehotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -8334,9 +9402,13 @@
         </is>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
-      </c>
-      <c r="H282" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Pondok_Rizky_Amalia</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -8390,9 +9462,13 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
-      </c>
-      <c r="H284" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Amalys_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -8446,9 +9522,13 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
-      </c>
-      <c r="H286" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Simpang_Borobudur</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -8502,9 +9582,13 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
-      </c>
-      <c r="H288" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Maharaja_homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -8530,9 +9614,13 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
-      </c>
-      <c r="H289" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/CAKRAWALA_HOMESTAY</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -8558,9 +9646,13 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/VIO_HOMESTAY_PANTAI_UNGAPAN</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -8586,9 +9678,13 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
-      </c>
-      <c r="H291" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ariesta_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -8642,9 +9738,13 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
-      </c>
-      <c r="H293" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Cakra_Residence_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -8670,9 +9770,13 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
-      </c>
-      <c r="H294" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D’rael_Guest_House_Syariah_Turen</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -8726,9 +9830,13 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
-      </c>
-      <c r="H296" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hnr_Homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -8754,9 +9862,13 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
-      </c>
-      <c r="H297" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Swun_Stay_Inn_@_Sawahan_Mitra_RedDoorz</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -8782,9 +9894,13 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0</v>
-      </c>
-      <c r="H298" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bobopod_Alun-Alun,_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -8810,9 +9926,13 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
-      </c>
-      <c r="H299" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Velodrome_Malang_2</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -8838,9 +9958,13 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
-      </c>
-      <c r="H300" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sentral_homestay</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -8866,9 +9990,13 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
-      </c>
-      <c r="H301" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_Omah_Wetan_Homestay_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -8894,9 +10022,13 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SO!_Boutique_Hostel</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -8922,9 +10054,13 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
-      </c>
-      <c r="H303" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Pelangi_Malang,_Kayutangan_Heritage</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -8950,9 +10086,13 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
-      </c>
-      <c r="H304" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Margosuko_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -8978,9 +10118,13 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>0</v>
-      </c>
-      <c r="H305" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_Grand_Palace_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -9006,9 +10150,13 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
-      </c>
-      <c r="H306" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Omah_Kalimosodo_RedPartner_near_Stasiun_Malang_Kota_Baru</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -9034,9 +10182,13 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
-      </c>
-      <c r="H307" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/M-Suite_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -9062,9 +10214,13 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
-      </c>
-      <c r="H308" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Granada_Syariah_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -9090,9 +10246,13 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>0</v>
-      </c>
-      <c r="H309" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griyo_Sultan_Agung_Guest_House_(Book_our_rooms_via_WhatsApp_Chat)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -9118,9 +10278,13 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
-      </c>
-      <c r="H310" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Backpacker_Pak_yon</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -9146,9 +10310,13 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
-      </c>
-      <c r="H311" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bedpackers_Hostel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -9174,9 +10342,13 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
-      </c>
-      <c r="H312" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_90383_Avisha_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -9202,9 +10374,13 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
-      </c>
-      <c r="H313" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Ratu_Boarding_House_&amp;_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -9258,9 +10434,13 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
-      </c>
-      <c r="H315" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_90319_Angler_Guest_House_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -9286,9 +10466,13 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>0</v>
-      </c>
-      <c r="H316" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/pandanwangi_homestay_syariah_(hotel_murah_malang)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -9314,9 +10498,13 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
-      </c>
-      <c r="H317" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Kartika_Graha</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -9342,9 +10530,13 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
-      </c>
-      <c r="H318" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Balai_Kota_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -9370,9 +10562,13 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>0</v>
-      </c>
-      <c r="H319" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Jalan_Kedawung</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -9398,9 +10594,13 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
-      </c>
-      <c r="H320" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Butik_Capsule_Hostel_WA_0813-1569-6413</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -9426,9 +10626,13 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>0</v>
-      </c>
-      <c r="H321" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_Safa_Baiti_Guest_House_Syari'ah</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -9454,9 +10658,13 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>0</v>
-      </c>
-      <c r="H322" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Shelter_Hostel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -9482,9 +10690,13 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>0</v>
-      </c>
-      <c r="H323" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/PENGINAPAN_DeWe</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -9510,9 +10722,13 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
-      </c>
-      <c r="H324" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Sanan_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -9538,9 +10754,13 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>0</v>
-      </c>
-      <c r="H325" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Merbabu_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -9566,9 +10786,13 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
-      </c>
-      <c r="H326" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RAGGEA_homestay</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -9594,9 +10818,13 @@
         </is>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
-      </c>
-      <c r="H327" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hasanah_Guesthouse_Suhat</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -9622,9 +10850,13 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>0</v>
-      </c>
-      <c r="H328" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Premium_@_Jalan_Cengkeh_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -9650,9 +10882,13 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
-      </c>
-      <c r="H329" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Reddoorz_Near_Universitas_Widyagama_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -9678,9 +10914,13 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>0</v>
-      </c>
-      <c r="H330" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Noura_Guest_House_Syariah_Cabang_Soekarno_Hatta</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -9706,9 +10946,13 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>0</v>
-      </c>
-      <c r="H331" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Taman_Indah_Homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -9734,9 +10978,13 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0</v>
-      </c>
-      <c r="H332" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SIMPANG_HOMESTAY_&amp;_KOZZ</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -9762,9 +11010,13 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0</v>
-      </c>
-      <c r="H333" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_near_Universitas_Negeri_Malang_2</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -9790,9 +11042,13 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>0</v>
-      </c>
-      <c r="H334" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Tripletree_Novon_Family_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -9818,9 +11074,13 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
-      </c>
-      <c r="H335" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_near_Politeknik_Negeri_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -9846,9 +11106,13 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
-      </c>
-      <c r="H336" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_2771_D'soetta</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -9874,9 +11138,13 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>0</v>
-      </c>
-      <c r="H337" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_@_Soekarno_Hatta_Indah_2</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -9902,9 +11170,13 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
-      </c>
-      <c r="H338" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_3350_Cozy_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -9930,9 +11202,13 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
-      </c>
-      <c r="H339" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Shanta_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -9986,9 +11262,13 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
-      </c>
-      <c r="H341" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_@_Kalpataru</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -10014,9 +11294,13 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
-      </c>
-      <c r="H342" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_near_RRI_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -10042,9 +11326,13 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>0</v>
-      </c>
-      <c r="H343" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Behomy_Inn_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -10098,9 +11386,13 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
-      </c>
-      <c r="H345" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Liberta_Hub_Singosari_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -10126,9 +11418,13 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
-      </c>
-      <c r="H346" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Aventree_Syariah_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -10154,9 +11450,13 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>0</v>
-      </c>
-      <c r="H347" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/DE_LAIA_INN_MALANG</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -10182,9 +11482,13 @@
         </is>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
-      </c>
-      <c r="H348" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Al_Thalib_8_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -10210,9 +11514,13 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
-      </c>
-      <c r="H349" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/YUTAKA_INN_Araya_Malang_Nugraha</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -10238,9 +11546,13 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0</v>
-      </c>
-      <c r="H350" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Grand_Kadaka_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -10266,9 +11578,13 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
-      </c>
-      <c r="H351" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_@_Riverside_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -10294,9 +11610,13 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
-      </c>
-      <c r="H352" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D'Fresh_Guest_House_and_Resto</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -10322,9 +11642,13 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
-      </c>
-      <c r="H353" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Griya_Harmoni_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -10350,9 +11674,13 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
-      </c>
-      <c r="H354" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_K10_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -10378,9 +11706,13 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0</v>
-      </c>
-      <c r="H355" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D'_soetta_guest_house</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -10406,9 +11738,13 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
-      </c>
-      <c r="H356" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Everyday_Smart_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -10434,9 +11770,13 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
-      </c>
-      <c r="H357" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_@_Karangploso_2</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -10462,9 +11802,13 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0</v>
-      </c>
-      <c r="H358" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Gatsu_Resort_RedPartner_@_Karangploso</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -10490,9 +11834,13 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
-      </c>
-      <c r="H359" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/De_Sapphire_Hasanah_Guesthouse</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -10518,9 +11866,13 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
-      </c>
-      <c r="H360" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/N_Sungkar_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -10546,9 +11898,13 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
-      </c>
-      <c r="H361" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/TOS_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -10574,9 +11930,13 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
-      </c>
-      <c r="H362" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/CITARUM_HOMESTAY_MALANG</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -10602,9 +11962,13 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
-      </c>
-      <c r="H363" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/éL_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -10630,9 +11994,13 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
-      </c>
-      <c r="H364" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Shanaya_Resort_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -10658,9 +12026,13 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
-      </c>
-      <c r="H365" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Grage_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -10686,9 +12058,13 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>0</v>
-      </c>
-      <c r="H366" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Airy_Singosari_Raya_Mondoroko_1_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -10714,9 +12090,13 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
-      </c>
-      <c r="H367" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Good_Village_Project_-_Malang_Voluntourism</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -10742,9 +12122,13 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>0</v>
-      </c>
-      <c r="H368" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lembah_Mbalong_Resort_Mitra_RedDoorz_Near_Exit_Tol_Singosari</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -10770,9 +12154,13 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
-      </c>
-      <c r="H369" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SPOT_ON_2689_Safira_Family_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -10798,9 +12186,13 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
-      </c>
-      <c r="H370" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Wisata_Paribendo_Lawang</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -10826,9 +12218,13 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>0</v>
-      </c>
-      <c r="H371" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rollaas_Hotel_and_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -10910,9 +12306,13 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
-      </c>
-      <c r="H374" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Arjuna</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -10938,9 +12338,13 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
-      </c>
-      <c r="H375" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OAK_Lawang</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -10966,9 +12370,13 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>0</v>
-      </c>
-      <c r="H376" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Buah_Naga</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -10994,9 +12402,13 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>0</v>
-      </c>
-      <c r="H377" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_90684_Happy_Homestay_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -11022,9 +12434,13 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
-      </c>
-      <c r="H378" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Niagara</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -11050,9 +12466,13 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0</v>
-      </c>
-      <c r="H379" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sri_maha_resort_in_teluk_asmara</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -11078,9 +12498,13 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
-      </c>
-      <c r="H380" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Penginapan_Pondok_Wisata_Berkah_Alam</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -11106,9 +12530,13 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0</v>
-      </c>
-      <c r="H381" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Guest_House_Madidihang_Pondokdadap_-_Sendang_Biru</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -11134,9 +12562,13 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0</v>
-      </c>
-      <c r="H382" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Asmara_Hills</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -11162,9 +12594,13 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
-      </c>
-      <c r="H383" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Maltan’s_Room</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -11190,9 +12626,13 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
-      </c>
-      <c r="H384" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_Pondok_Bamboe_Sendang_Biru</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -11218,9 +12658,13 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0</v>
-      </c>
-      <c r="H385" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Safa_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -11246,9 +12690,13 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0</v>
-      </c>
-      <c r="H386" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_near_Exit_Tol_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -11274,9 +12722,13 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0</v>
-      </c>
-      <c r="H387" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Javana_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -11302,9 +12754,13 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0</v>
-      </c>
-      <c r="H388" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sawojajar_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -11330,9 +12786,13 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0</v>
-      </c>
-      <c r="H389" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/K15_Exclusive</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -11358,9 +12818,13 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0</v>
-      </c>
-      <c r="H390" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Plus_near_Malang_Airport</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -11386,9 +12850,13 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>0</v>
-      </c>
-      <c r="H391" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Jacatra_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -11414,9 +12882,13 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0</v>
-      </c>
-      <c r="H392" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Morse_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -11442,9 +12914,13 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>0</v>
-      </c>
-      <c r="H393" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/SOWAN_Boutique_Guest_House_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -11470,9 +12946,13 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>0</v>
-      </c>
-      <c r="H394" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Wilis_Indah_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -11498,9 +12978,13 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>0</v>
-      </c>
-      <c r="H395" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Araya_Family_Club_House</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -11526,9 +13010,13 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
-      </c>
-      <c r="H396" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Se.nandung_Living_&amp;_Space</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -11554,9 +13042,13 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>0</v>
-      </c>
-      <c r="H397" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Nova_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -11582,9 +13074,13 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>0</v>
-      </c>
-      <c r="H398" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Guest_House_Araya</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -11610,9 +13106,13 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>0</v>
-      </c>
-      <c r="H399" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Se.juk_ResidencePremiere</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -11638,9 +13138,13 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>0</v>
-      </c>
-      <c r="H400" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Victoria_Boutique_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -11694,9 +13198,13 @@
         </is>
       </c>
       <c r="G402" t="n">
-        <v>0</v>
-      </c>
-      <c r="H402" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Montana_Dua_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -11722,9 +13230,13 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>0</v>
-      </c>
-      <c r="H403" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Swiss-Belinn_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -11750,9 +13262,13 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>0</v>
-      </c>
-      <c r="H404" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/nDalem_Kilen_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -11778,9 +13294,13 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>0</v>
-      </c>
-      <c r="H405" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/D'Paragon_Songgolangit_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -11806,9 +13326,13 @@
         </is>
       </c>
       <c r="G406" t="n">
-        <v>0</v>
-      </c>
-      <c r="H406" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Fariz_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -11834,9 +13358,13 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>0</v>
-      </c>
-      <c r="H407" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Karolin_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -11862,9 +13390,13 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>0</v>
-      </c>
-      <c r="H408" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Solaris_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -11890,9 +13422,13 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>0</v>
-      </c>
-      <c r="H409" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Padi_Homestay_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -11918,9 +13454,13 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>0</v>
-      </c>
-      <c r="H410" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Syariah_Nusantara</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -11946,9 +13486,13 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>0</v>
-      </c>
-      <c r="H411" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Seruni_Lawang</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -11974,9 +13518,13 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>0</v>
-      </c>
-      <c r="H412" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Tawangsari,_HOSTEL_&amp;_RESORT</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -12002,9 +13550,13 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>0</v>
-      </c>
-      <c r="H413" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/MADOR_Malang_Dorm_Hostel</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -12030,9 +13582,13 @@
         </is>
       </c>
       <c r="G414" t="n">
-        <v>0</v>
-      </c>
-      <c r="H414" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Kampung_Warna_Warni</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -12058,9 +13614,13 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0</v>
-      </c>
-      <c r="H415" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Urbanview_Hotel_de_Kopen_Malang_by_RedDoorz</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -12086,9 +13646,13 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>0</v>
-      </c>
-      <c r="H416" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Dewarna_Sutoyo_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -12114,9 +13678,13 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>0</v>
-      </c>
-      <c r="H417" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/GRESS_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -12142,9 +13710,13 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>0</v>
-      </c>
-      <c r="H418" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Gajahmada_Graha</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -12198,9 +13770,13 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0</v>
-      </c>
-      <c r="H420" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Asri_Home_Stay</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -12226,9 +13802,13 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0</v>
-      </c>
-      <c r="H421" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/The_Aliante_Hotel_&amp;_Convention_Center</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -12254,9 +13834,13 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>0</v>
-      </c>
-      <c r="H422" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/THE_1O1_Malang_OJ</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -12282,9 +13866,13 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>0</v>
-      </c>
-      <c r="H423" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lily_Guest_House_Syariah_RedPartner</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -12338,9 +13926,13 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
-      </c>
-      <c r="H425" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Sans_Hotel_La_Vida_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -12366,9 +13958,13 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>0</v>
-      </c>
-      <c r="H426" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Plum_Dreamscape_Inan_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -12394,9 +13990,13 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>0</v>
-      </c>
-      <c r="H427" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Splendid_Inn_Hotel</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -12422,9 +14022,13 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>0</v>
-      </c>
-      <c r="H428" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Amaris_Hotel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -12450,9 +14054,13 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>0</v>
-      </c>
-      <c r="H429" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Junggo_Tentrem</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -12478,9 +14086,13 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>0</v>
-      </c>
-      <c r="H430" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/BeSS_Resort_and_Waterpark</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -12506,9 +14118,13 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>0</v>
-      </c>
-      <c r="H431" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Zzz_Hostel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -12534,9 +14150,13 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>0</v>
-      </c>
-      <c r="H432" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Neomi_Homestay_Malang_(CV.Neomi_perdana_sukse)</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -12562,9 +14182,13 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>0</v>
-      </c>
-      <c r="H433" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_near_Malang_Creative_Center</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -12590,9 +14214,13 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>0</v>
-      </c>
-      <c r="H434" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Djoglo_Luxury_Bungalow</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -12618,9 +14246,13 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>0</v>
-      </c>
-      <c r="H435" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Hotel_Grand_Cakra</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -12646,9 +14278,13 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>0</v>
-      </c>
-      <c r="H436" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Jardin_Smart_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -12674,9 +14310,13 @@
         </is>
       </c>
       <c r="G437" t="n">
-        <v>0</v>
-      </c>
-      <c r="H437" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rumah_Kita_2_(_Penginapan_Harian_dan_Sales)</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -12702,9 +14342,13 @@
         </is>
       </c>
       <c r="G438" t="n">
-        <v>0</v>
-      </c>
-      <c r="H438" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_1289_Cbr_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -12730,9 +14374,13 @@
         </is>
       </c>
       <c r="G439" t="n">
-        <v>0</v>
-      </c>
-      <c r="H439" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_3803_Hotel_Wonojati_Syariah_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -12758,9 +14406,13 @@
         </is>
       </c>
       <c r="G440" t="n">
-        <v>0</v>
-      </c>
-      <c r="H440" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Wisma_Air_Mancur_Malang_Syariah_Mitra_RedDoorz</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -12786,9 +14438,13 @@
         </is>
       </c>
       <c r="G441" t="n">
-        <v>0</v>
-      </c>
-      <c r="H441" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Pondok_Tubing_Poncokusumo_Syariah_RedPartner</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -12842,9 +14498,13 @@
         </is>
       </c>
       <c r="G443" t="n">
-        <v>0</v>
-      </c>
-      <c r="H443" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Semeru_Hostel_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -12870,9 +14530,13 @@
         </is>
       </c>
       <c r="G444" t="n">
-        <v>0</v>
-      </c>
-      <c r="H444" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Rani_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -12898,9 +14562,13 @@
         </is>
       </c>
       <c r="G445" t="n">
-        <v>0</v>
-      </c>
-      <c r="H445" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Lembah_Tumpang_Resort</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -12926,9 +14594,13 @@
         </is>
       </c>
       <c r="G446" t="n">
-        <v>0</v>
-      </c>
-      <c r="H446" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OMAH_JOGLO_BUGIS</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -12954,9 +14626,13 @@
         </is>
       </c>
       <c r="G447" t="n">
-        <v>0</v>
-      </c>
-      <c r="H447" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Fellas_Inn</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -12982,9 +14658,13 @@
         </is>
       </c>
       <c r="G448" t="n">
-        <v>0</v>
-      </c>
-      <c r="H448" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/RedDoorz_Syariah_@_Danau_Kerinci_Sawojajar</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -13010,9 +14690,13 @@
         </is>
       </c>
       <c r="G449" t="n">
-        <v>0</v>
-      </c>
-      <c r="H449" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Velodrome_Family_House</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -13038,9 +14722,13 @@
         </is>
       </c>
       <c r="G450" t="n">
-        <v>0</v>
-      </c>
-      <c r="H450" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Bima_Guest_House</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -13066,9 +14754,13 @@
         </is>
       </c>
       <c r="G451" t="n">
-        <v>0</v>
-      </c>
-      <c r="H451" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Millennial_House</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -13094,9 +14786,13 @@
         </is>
       </c>
       <c r="G452" t="n">
-        <v>0</v>
-      </c>
-      <c r="H452" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_886_Omahku_Asri_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -13122,9 +14818,13 @@
         </is>
       </c>
       <c r="G453" t="n">
-        <v>0</v>
-      </c>
-      <c r="H453" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Gita_Homestay_Malang</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -13150,9 +14850,13 @@
         </is>
       </c>
       <c r="G454" t="n">
-        <v>0</v>
-      </c>
-      <c r="H454" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/OYO_2295_Daffi_Family_Residence</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -13178,9 +14882,13 @@
         </is>
       </c>
       <c r="G455" t="n">
-        <v>0</v>
-      </c>
-      <c r="H455" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Convention_Hall_Bess_Resort_&amp;_Waterpark</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -13206,9 +14914,13 @@
         </is>
       </c>
       <c r="G456" t="n">
-        <v>0</v>
-      </c>
-      <c r="H456" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Villa_Girli_Lawang</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -13234,9 +14946,13 @@
         </is>
       </c>
       <c r="G457" t="n">
-        <v>0</v>
-      </c>
-      <c r="H457" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_Pantai_Lenggoksono_-_Banyu_Anjlok</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -13262,9 +14978,13 @@
         </is>
       </c>
       <c r="G458" t="n">
-        <v>0</v>
-      </c>
-      <c r="H458" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/tumpang_camp_adventures</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -13290,9 +15010,13 @@
         </is>
       </c>
       <c r="G459" t="n">
-        <v>0</v>
-      </c>
-      <c r="H459" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Chalet_Bromo_Restaurant_and_Lounge</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -13318,9 +15042,13 @@
         </is>
       </c>
       <c r="G460" t="n">
-        <v>0</v>
-      </c>
-      <c r="H460" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Glamping_Malang_Dreamland</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -13346,9 +15074,13 @@
         </is>
       </c>
       <c r="G461" t="n">
-        <v>0</v>
-      </c>
-      <c r="H461" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Wisma_Djokorio_Syariah</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -13374,9 +15106,13 @@
         </is>
       </c>
       <c r="G462" t="n">
-        <v>0</v>
-      </c>
-      <c r="H462" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/NAMIRA_HOMESTAY</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -13402,9 +15138,13 @@
         </is>
       </c>
       <c r="G463" t="n">
-        <v>0</v>
-      </c>
-      <c r="H463" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_Bu_Pit</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -13430,9 +15170,13 @@
         </is>
       </c>
       <c r="G464" t="n">
-        <v>0</v>
-      </c>
-      <c r="H464" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/De'forest_Rest_Area</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -13458,9 +15202,13 @@
         </is>
       </c>
       <c r="G465" t="n">
-        <v>0</v>
-      </c>
-      <c r="H465" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Puspa_Homestay_Gubugklakah</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -13486,9 +15234,13 @@
         </is>
       </c>
       <c r="G466" t="n">
-        <v>0</v>
-      </c>
-      <c r="H466" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Panglipuran_Homestay</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -13514,9 +15266,13 @@
         </is>
       </c>
       <c r="G467" t="n">
-        <v>0</v>
-      </c>
-      <c r="H467" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Gubug_bromo</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -13542,9 +15298,13 @@
         </is>
       </c>
       <c r="G468" t="n">
-        <v>0</v>
-      </c>
-      <c r="H468" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>GAMBAR/hotel/Homestay_Maria</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
